--- a/tools/xlsform_samples/SWLS.xlsx
+++ b/tools/xlsform_samples/SWLS.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -694,84 +694,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SWLS_scoring</t>
+          <t>SWLS_swlsscore</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>swlsscore (sum_coded)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>${swls1} + ${swls2} + ${swls3} + ${swls4} + ${swls5}</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SWLS_swlsscore</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>swlsscore (sum_coded)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>${swls1} + ${swls2} + ${swls3} + ${swls4} + ${swls5}</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SWLS_scoring</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/SWLS.xlsx
+++ b/tools/xlsform_samples/SWLS.xlsx
@@ -934,7 +934,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/SWLS.xlsx
+++ b/tools/xlsform_samples/SWLS.xlsx
@@ -442,12 +442,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -524,32 +524,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>swls1</t>
+          <t>question_head</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>In most ways my life is close to my ideal.</t>
+          <t>Below are five statements that you may agree or disagree with. Using the scale below, indicate your agreement with each item by clicking the appropriate selection. Please be open and honest in your responding.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -563,12 +555,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>swls2</t>
+          <t>swls1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The conditions of my life are excellent.</t>
+          <t>In most ways my life is close to my ideal.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -597,12 +589,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>swls3</t>
+          <t>swls2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>I am satisfied with my life.</t>
+          <t>The conditions of my life are excellent.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -631,12 +623,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>swls4</t>
+          <t>swls3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>So far I have gotten the important things I want in life.</t>
+          <t>I am satisfied with my life.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -665,12 +657,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>swls5</t>
+          <t>swls4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>If I could live my life over, I would change almost nothing.</t>
+          <t>So far I have gotten the important things I want in life.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -694,32 +686,66 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SWLS_swlsscore</t>
+          <t>swls5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>swlsscore (sum_coded)</t>
+          <t>If I could live my life over, I would change almost nothing.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>${swls1} + ${swls2} + ${swls3} + ${swls4} + ${swls5}</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SWLS_swlsscore</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>swlsscore (sum_coded)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>${swls1} + ${swls2} + ${swls3} + ${swls4} + ${swls5}</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
